--- a/templates/resource_config.xlsx
+++ b/templates/resource_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="600" windowWidth="50415" windowHeight="16425"/>
+    <workbookView xWindow="630" yWindow="600" windowWidth="50415" windowHeight="16425" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="47">
   <si>
     <t>section_id</t>
   </si>
@@ -48,112 +48,123 @@
     <t>28</t>
   </si>
   <si>
-    <t>标题</t>
-  </si>
-  <si>
     <t>副标题</t>
   </si>
   <si>
-    <t>简介</t>
+    <t>字幕</t>
+  </si>
+  <si>
+    <t>网盘名称</t>
+  </si>
+  <si>
+    <t>下载链接</t>
+  </si>
+  <si>
+    <t>解压密码</t>
+  </si>
+  <si>
+    <t>支持格式</t>
+  </si>
+  <si>
+    <t>名侦探柯南：时计坍塌的摩天楼</t>
+  </si>
+  <si>
+    <t>第1部</t>
+  </si>
+  <si>
+    <t>建筑大亨的摩天楼遭到炸弹威胁，小学生侦探柯南必须在有限的时间内找出真凶，阻止爆炸发生...</t>
+  </si>
+  <si>
+    <t>日语</t>
+  </si>
+  <si>
+    <t>中文</t>
+  </si>
+  <si>
+    <t>百度网盘</t>
+  </si>
+  <si>
+    <t>https://pan.baidu.com/s/xxxxx?pwd=xxxx</t>
+  </si>
+  <si>
+    <t>abcd1234</t>
+  </si>
+  <si>
+    <t>mp4,mkv</t>
+  </si>
+  <si>
+    <t>../res/film/推理系列/柯南/conan00.webp</t>
+  </si>
+  <si>
+    <t>金田一少年事件簿：瞳孔之中的黑影</t>
+  </si>
+  <si>
+    <t>电影版</t>
+  </si>
+  <si>
+    <t>神秘村落连续杀人案，金田一需要在极端环境中破案...</t>
+  </si>
+  <si>
+    <t>TODO</t>
+  </si>
+  <si>
+    <t>xyz98765</t>
+  </si>
+  <si>
+    <t>mkv</t>
+  </si>
+  <si>
+    <t>../res/film/推理系列/金田一/title1.webp</t>
+  </si>
+  <si>
+    <t>数码宝贝：小镇英雄</t>
+  </si>
+  <si>
+    <t>小学生进入数码世界，与数码宝贝一起对抗邪恶势力...</t>
+  </si>
+  <si>
+    <t>digi1234</t>
+  </si>
+  <si>
+    <t>mp4</t>
+  </si>
+  <si>
+    <t>1997-11-21</t>
+  </si>
+  <si>
+    <t>../res/film/动画系列/数码暴龙/title01.webp</t>
+  </si>
+  <si>
+    <t>概要</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>语言</t>
-  </si>
-  <si>
-    <t>字幕</t>
-  </si>
-  <si>
-    <t>网盘名称</t>
-  </si>
-  <si>
-    <t>下载链接</t>
-  </si>
-  <si>
-    <t>解压密码</t>
-  </si>
-  <si>
-    <t>支持格式</t>
-  </si>
-  <si>
-    <t>上映时间</t>
-  </si>
-  <si>
-    <t>海报路径</t>
-  </si>
-  <si>
-    <t>名侦探柯南：时计坍塌的摩天楼</t>
-  </si>
-  <si>
-    <t>第1部</t>
-  </si>
-  <si>
-    <t>建筑大亨的摩天楼遭到炸弹威胁，小学生侦探柯南必须在有限的时间内找出真凶，阻止爆炸发生...</t>
-  </si>
-  <si>
-    <t>日语</t>
-  </si>
-  <si>
-    <t>中文</t>
-  </si>
-  <si>
-    <t>百度网盘</t>
-  </si>
-  <si>
-    <t>https://pan.baidu.com/s/xxxxx?pwd=xxxx</t>
-  </si>
-  <si>
-    <t>abcd1234</t>
-  </si>
-  <si>
-    <t>mp4,mkv</t>
-  </si>
-  <si>
-    <t>1997-04-19</t>
-  </si>
-  <si>
-    <t>../res/film/推理系列/柯南/conan00.webp</t>
-  </si>
-  <si>
-    <t>金田一少年事件簿：瞳孔之中的黑影</t>
-  </si>
-  <si>
-    <t>电影版</t>
-  </si>
-  <si>
-    <t>神秘村落连续杀人案，金田一需要在极端环境中破案...</t>
-  </si>
-  <si>
-    <t>TODO</t>
-  </si>
-  <si>
-    <t>xyz98765</t>
-  </si>
-  <si>
-    <t>mkv</t>
-  </si>
-  <si>
-    <t>2006-11-18</t>
-  </si>
-  <si>
-    <t>../res/film/推理系列/金田一/title1.webp</t>
-  </si>
-  <si>
-    <t>数码宝贝：小镇英雄</t>
-  </si>
-  <si>
-    <t>小学生进入数码世界，与数码宝贝一起对抗邪恶势力...</t>
-  </si>
-  <si>
-    <t>digi1234</t>
-  </si>
-  <si>
-    <t>mp4</t>
-  </si>
-  <si>
-    <t>1997-11-21</t>
-  </si>
-  <si>
-    <t>../res/film/动画系列/数码暴龙/title01.webp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡片页脚</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上映时间：2011-03-28</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上映时间：2006-11-18</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>封面图片路径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主标题</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>目录路径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -565,122 +576,125 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="40" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="19.625" customWidth="1"/>
+    <col min="5" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="F2" t="s">
         <v>20</v>
       </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -691,87 +705,90 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="40" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>20</v>
+      <c r="L1" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" t="s">
         <v>35</v>
       </c>
-      <c r="H2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" t="s">
-        <v>44</v>
-      </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>36</v>
+      </c>
+      <c r="L2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/templates/resource_config.xlsx
+++ b/templates/resource_config.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
-    <sheet name="推理探案系列" sheetId="2" r:id="rId2"/>
-    <sheet name="数码暴龙系列" sheetId="3" r:id="rId3"/>
+    <sheet name="世界奇妙物语系列" sheetId="2" r:id="rId2"/>
+    <sheet name="藤原龙也系列" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
